--- a/玩家资料模板.xlsx
+++ b/玩家资料模板.xlsx
@@ -3,20 +3,20 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28800" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="玩家资料" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="21">
+  <fonts count="3">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -34,344 +34,20 @@
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF0000FF"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="18"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C6500"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="1"/>
-      <sz val="11"/>
+      <sz val="9"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -379,306 +55,16 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -1031,6 +417,7 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -1040,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:M34"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col width="27.725" customWidth="1" min="1" max="1"/>
-    <col width="32.1833333333333" customWidth="1" min="2" max="2"/>
-    <col width="42.0916666666667" customWidth="1" min="6" max="6"/>
-    <col width="70.25" customWidth="1" min="9" max="9"/>
+    <col width="27.7265625" customWidth="1" min="1" max="1"/>
+    <col width="32.1796875" customWidth="1" min="2" max="2"/>
+    <col width="42.08984375" customWidth="1" min="6" max="6"/>
+    <col width="70.26953125" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1124,32 +511,47 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>diaolelao3962是猫娘</t>
+          <t>我是Diaolelao3962</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>纯净输出</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>轻舟舟</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>陶xx</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>注重文明用语，被坑后直接金钱惩罚，冷静务实且讲原则。</t>
+          <t>心疼钱包且务实，自嘲远离少爷生活，是留守服务器独撑大局的孤独基石。</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>学业压力大的学生，感到孤独，频繁刷屏求关注，情绪低落且有些神经质。</t>
+          <t>务实的技术派，注重效率与成本控制，对资源消耗敏感，自称正在开发项目。</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>嘴硬心软，一边吐槽兄弟一边认真写作业，怕开学查作业要完蛋。</t>
+          <t>注重性价比和效率，对付费和延迟敏感，对AI工具表现挑剔且务实，追求快速解决问题。</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>喜爱玩音乐，感情直率，经常用夸张语气和兄弟们互动，是个活跃气氛的玩家。</t>
+          <t>精打细算，得知免费方案后对之前花一百多元感到错愕。</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>点歌随性，疑神疑鬼爱开玩笑，自称兄弟众多且热衷于整活。</t>
+          <t>热心又好奇，发现新玩具第一时间分享，可惜朋友kevin是个跑路选手。</t>
         </is>
       </c>
     </row>
@@ -1164,29 +566,39 @@
           <t>fuud是小猫娘</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>无极</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>无机</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>话少且反应简短，常发语气词和问号表达惊讶或困惑，交流风格随意。</t>
+          <t>反应夸张，满屏颜文字，嘴碎爱吐槽，自称Gaygay记，脑回路清奇。</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>关注战斗数值和延迟，随性简短，语气词丰富，情绪反应直接。</t>
+          <t>反应夸张，擅长用颜文字和语气词制造幽默氛围，情绪表达丰富且充满戏剧性。</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>迷糊又急性子，经常看错字或打错字，对服务器卡顿和环境反应敏感。</t>
+          <t>乱码喷子，爱用表情和脏话刷屏。</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>直率简短的游戏玩家，在意伤害数值，遇到脏话会吐槽反感。</t>
+          <t>语气跳跃，频繁发表情和问号，求教红石时礼貌喊大佬，建建筑却因领土限制被拒，最后带点无厘头的自嘲。</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>爱发短句吐槽，常喊坏AI，爱怪笑桀桀桀，热衷打架嫌怪太肉。</t>
+          <t>爱刷屏玩梗，情绪起伏大，遇事慌乱求大佬。</t>
         </is>
       </c>
     </row>
@@ -1210,14 +622,34 @@
           <t>Be_kong</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>大肥鱼吃白饭中</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>以法治言论恶搞互动，被调侃“AI魔了”也不改，是个用法律条文整活且心态稳的乐子人。</t>
+          <t>专注建模，灵感多但输出慢，懂技术插件。</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>爱玩主人猫娘角色扮演，语气调皮爱复读，自称超威还追问谁更可爱。</t>
+          <t>电脑压力大但忙不过来，思维活跃，对数字和配置限制敏感，用颜文字掩饰慌乱。</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>沉迷折腾AI工具与服务器优化，对性能瓶颈很敏感，语气轻松带点调皮。</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>对AI工具很熟悉，关注技术社区，能准确说出DeepSeek和OpenCode Zen等具体产品。</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>关注技术细节，注重逻辑与验证。性格幽默，脑洞大，思维活跃。</t>
         </is>
       </c>
     </row>
@@ -1253,27 +685,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>嘴硬心软，爱玩梗。对八卦反应灵敏，面对吐槽时表现出典型的无奈与无语。</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>语气软萌爱卖萌，但会主动询问他人是否需要烈焰棒，看似迷糊实则细心。</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>被卡刷怪困扰，敏锐怀疑他人搬运消息，并热心提供服务器权限配置建议。</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t>说话随性，表情符号丰富，思维跳跃，对物品合成有自己的见解。</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>懂红石技术，说话简短直接，习惯用颜文字和表情，对游戏机制有自己见解。</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>观察力敏锐，热衷于探索红石机关，对复杂的机制感到困惑时用颜文字表达无语。</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>思维跳跃，爱在数字谜题和音乐请求间切换，用摩斯密码卖萌，是个脑洞大开的乐子人。</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>被延迟和机制折腾得烦躁又无奈，有点小情绪但还在努力理解规则。</t>
         </is>
       </c>
     </row>
@@ -1297,6 +729,46 @@
           <t>astronsol</t>
         </is>
       </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>瓜瓜</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>脆刷刷</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>雷霆大田</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>爱开黄腔，记性极差，聊天随性脱线。</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>喜欢追忆学生时代暗恋往事，说话随性跳跃，对细节记忆模糊但情感真挚。</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>心思细腻，有点闷骚幽默。和小学同学从一年级一路同班到现在的“奇迹”缘分，还有段暗恋往事。</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>喜欢讲八卦和情感经历，但对单相思有些无奈自嘲，说话跳跃随性。</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>脑洞大开又三分钟热度，爱玩神秘梗，讲到一半直接去睡觉，是个活泼又随意的沙雕玩家。</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1328,6 +800,46 @@
           <t>RoiAsn</t>
         </is>
       </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>轻舟</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>等待僵尸</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>急躁且目的明确，急需命名牌给村民起名，表现出强烈的行动力和对效率的追求。</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>沉默寡言，沟通断续且直接，常在关键节点（如计数、询问资源）时精准切入，展现出务实的观察者特质。</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>话少高冷，发言简短，似乎擅长开运和矿车运输，但运气或状态不太好容易死。</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>脾气急躁，说话简短直接，常爆粗口，急于等队友带僵尸。</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>思维跳跃，说话断续，自称知道12核配置，晚上约着帮忙处理僵尸。</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1335,6 +847,11 @@
           <t>DiaoHelper</t>
         </is>
       </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>我是qingzhouf101</t>
+        </is>
+      </c>
       <c r="C16" t="inlineStr">
         <is>
           <t>猫娘</t>
@@ -1345,29 +862,34 @@
           <t>Diaolelao3962</t>
         </is>
       </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Fuud</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>暴躁直率，语言粗俗且带攻击性，对技术配置和专业知识均有涉猎。</t>
+          <t>沉迷点歌听歌，对《甲乙丙丁》情有独钟，甚至和别人撞曲，完全没注意到系统报错和安装mod的提示。</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>喜欢玩梗和抽象聊天，情绪跳跃大，会调侃队友又突然煽情，发言毫无逻辑。</t>
+          <t>爱点歌，品味独特，喜欢李佳薇和火羊瞌睡了的歌曲。</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>数据异常，疑似测试代码或故障输入，无法提炼玩家性格。</t>
+          <t>有点小资情调，爱点伤感情歌，可惜服务器没装音乐mod，歌始终放不出来，自带倒霉属性。</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>直率暴躁，喜欢怼人，逻辑清奇且毫不客气，口头禅是让人“说人话”。</t>
+          <t>爱点歌听歌，品味偏感性，多次点播李佳薇和张韶涵的歌，是服务器里的音乐爱好者。</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>说话直率，脾气火爆，爱骂人但讲义气，有点小脾气又不失风趣。</t>
+          <t>热衷于在服务器音乐机器人处点歌，偏爱李佳薇和火羊瞌睡了的歌曲，但常因技术配置问题听不到完整曲目。</t>
         </is>
       </c>
     </row>
@@ -1377,6 +899,11 @@
           <t>yuezuiyin</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>有点倒霉但心态不错，为了找烈焰笼跑图摸到了一个让人无奈又有点可爱的结果。</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1492,9 +1019,88 @@
           <t>SR_Gardenia</t>
         </is>
       </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>美西螈</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>爱用问号表达困惑，对聊天对象是玩家还是AI充满怀疑。</t>
+          <t>敷衍冷淡，惜字如金，对话时常用省略号和问号表达无语或质疑。</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>说话简短带语气词，语气随意且略显敷衍，像是刚发现熟人后的随性回应。</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>遇到难题会直接摆烂说没招，但观察力敏锐，能注意到美西螈互动的细节。</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>思维跳跃且碎片化，常用问号表达疑惑，对游戏机制有独特理解，关心现实用餐与游戏进度。</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>爱摆烂，用问号应付聊天，自称有蜜蜂，逻辑清奇。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>beifeng13597</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>吐槽犀利，关注游戏更新细节，遇到意外情况会喊大佬来救场。</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>吐槽地图设计破坏观感，直言不讳，随即随性选址继续建造。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>zhe_4101</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>awa</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>喜欢用拟声词和碎片化表达，语气搞怪随意，可能正在带小白爬高。</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>语气随性简短，自称建筑相关，有点卖萌，对资源索取随意。</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>热心靠谱，擅长建筑运输规划，会主动提醒陷阱细节和夜间行动策略。</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>关注服务器更新细节，对 Minecraft 新特性有明确追求，语言风格碎片化。</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>热情开朗，说话带语气词，关注服务器动态，中英文混用。</t>
         </is>
       </c>
     </row>
